--- a/Painel_Academico_PUCPR.xlsx
+++ b/Painel_Academico_PUCPR.xlsx
@@ -747,7 +747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="61" customWidth="1" min="1" max="1"/>
@@ -827,6 +827,11 @@
           <t>SOMATIVA 1B: Negociação ECDH (RA1)</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:59:59Z</t>
+        </is>
+      </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
@@ -847,6 +852,11 @@
           <t>SOMATIVA 1C: Modelo criptográfico híbrido do PGP (RA1)</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:59:59Z</t>
+        </is>
+      </c>
       <c r="D4" t="n">
         <v>3</v>
       </c>
@@ -864,11 +874,16 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SOMATIVA 2A: Autenticação com SALT (RA2)</t>
+          <t>Avaliação Teórica do RA1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-09-22T12:40:00Z</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -877,18 +892,18 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://pucpr.instructure.com/courses/71912/assignments/338793</t>
+          <t>https://pucpr.instructure.com/courses/71912/assignments/358841</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SOMATIVA 2B: Autenticação Mútua e Challenge -SCRAM (RA 2)</t>
+          <t>SOMATIVA 2A: Autenticação com SALT (RA2)</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -897,18 +912,18 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://pucpr.instructure.com/courses/71912/assignments/338794</t>
+          <t>https://pucpr.instructure.com/courses/71912/assignments/338793</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SOMATIVA 4: Aplicações com API TLS (RA2)</t>
+          <t>SOMATIVA 2B: Autenticação Mútua e Challenge -SCRAM (RA 2)</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -917,18 +932,18 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://pucpr.instructure.com/courses/71912/assignments/338796</t>
+          <t>https://pucpr.instructure.com/courses/71912/assignments/338794</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TDE 1: Identificação por assinatura digital (RA3)</t>
+          <t>SOMATIVA 4: Aplicações com API TLS (RA2)</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -937,14 +952,14 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://pucpr.instructure.com/courses/71912/assignments/338797</t>
+          <t>https://pucpr.instructure.com/courses/71912/assignments/338796</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TDE 2: Análise de uma captura HTTPS (RA3)</t>
+          <t>TDE 1: Identificação por assinatura digital (RA3)</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -957,25 +972,45 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://pucpr.instructure.com/courses/71912/assignments/338798</t>
+          <t>https://pucpr.instructure.com/courses/71912/assignments/338797</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>TDE 2: Análise de uma captura HTTPS (RA3)</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://pucpr.instructure.com/courses/71912/assignments/338798</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t xml:space="preserve">SOMATIVA 3: Criação e uso de Certificados Digitais (RA 3) </t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D11" t="n">
         <v>4</v>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>https://pucpr.instructure.com/courses/71912/assignments/338795</t>
         </is>
@@ -1156,7 +1191,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -1220,7 +1255,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1493,6 +1528,11 @@
           <t>SOMATIVA 1B: Negociação ECDH (RA1)</t>
         </is>
       </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:59:59Z</t>
+        </is>
+      </c>
       <c r="D11" t="n">
         <v>2</v>
       </c>
@@ -1513,6 +1553,11 @@
           <t>SOMATIVA 1C: Modelo criptográfico híbrido do PGP (RA1)</t>
         </is>
       </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:59:59Z</t>
+        </is>
+      </c>
       <c r="D12" t="n">
         <v>3</v>
       </c>
@@ -1530,15 +1575,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SOMATIVA 2A: Autenticação com SALT (RA2)</t>
+          <t>Avaliação Teórica do RA1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-09-22T12:40:00Z</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://pucpr.instructure.com/courses/71912/assignments/338793</t>
+          <t>https://pucpr.instructure.com/courses/71912/assignments/358841</t>
         </is>
       </c>
     </row>
@@ -1550,15 +1600,15 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SOMATIVA 2B: Autenticação Mútua e Challenge -SCRAM (RA 2)</t>
+          <t>SOMATIVA 2A: Autenticação com SALT (RA2)</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://pucpr.instructure.com/courses/71912/assignments/338794</t>
+          <t>https://pucpr.instructure.com/courses/71912/assignments/338793</t>
         </is>
       </c>
     </row>
@@ -1570,15 +1620,15 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SOMATIVA 4: Aplicações com API TLS (RA2)</t>
+          <t>SOMATIVA 2B: Autenticação Mútua e Challenge -SCRAM (RA 2)</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://pucpr.instructure.com/courses/71912/assignments/338796</t>
+          <t>https://pucpr.instructure.com/courses/71912/assignments/338794</t>
         </is>
       </c>
     </row>
@@ -1590,15 +1640,15 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>TDE 1: Identificação por assinatura digital (RA3)</t>
+          <t>SOMATIVA 4: Aplicações com API TLS (RA2)</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://pucpr.instructure.com/courses/71912/assignments/338797</t>
+          <t>https://pucpr.instructure.com/courses/71912/assignments/338796</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1660,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>TDE 2: Análise de uma captura HTTPS (RA3)</t>
+          <t>TDE 1: Identificação por assinatura digital (RA3)</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1618,7 +1668,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://pucpr.instructure.com/courses/71912/assignments/338798</t>
+          <t>https://pucpr.instructure.com/courses/71912/assignments/338797</t>
         </is>
       </c>
     </row>
@@ -1630,13 +1680,33 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>TDE 2: Análise de uma captura HTTPS (RA3)</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>https://pucpr.instructure.com/courses/71912/assignments/338798</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Criptografia Aplicada</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t xml:space="preserve">SOMATIVA 3: Criação e uso de Certificados Digitais (RA 3) </t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="D19" t="n">
         <v>4</v>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>https://pucpr.instructure.com/courses/71912/assignments/338795</t>
         </is>

--- a/Painel_Academico_PUCPR.xlsx
+++ b/Painel_Academico_PUCPR.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -504,25 +504,75 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>TDE 2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-10-24T02:59:59Z</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://pucpr.instructure.com/courses/71926/assignments/352623</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>PjBL Parte 1</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>2026-08-22T02:59:59Z</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D4" t="n">
         <v>40</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>https://pucpr.instructure.com/courses/71926/assignments/353921</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>PjBL Parte 2</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-10-31T02:59:59Z</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>40</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://pucpr.instructure.com/courses/71926/assignments/360142</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1197,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1255,7 +1305,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1325,70 +1375,70 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PjBL Parte 1</t>
+          <t>TDE 2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-08-22T02:59:59Z</t>
+          <t>2026-10-24T02:59:59Z</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://pucpr.instructure.com/courses/71926/assignments/353921</t>
+          <t>https://pucpr.instructure.com/courses/71926/assignments/352623</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Conectividade e Sistemas Ciberfísicos</t>
+          <t>Arquitetura de Banco de Dados</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>TDE 1 - Trabalho Discente Efetivo</t>
+          <t>PjBL Parte 1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-09-14T02:59:59Z</t>
+          <t>2026-08-22T02:59:59Z</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://pucpr.instructure.com/courses/71920/assignments/342276</t>
+          <t>https://pucpr.instructure.com/courses/71926/assignments/353921</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Conectividade e Sistemas Ciberfísicos</t>
+          <t>Arquitetura de Banco de Dados</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Atividade1 -  Wireshark</t>
+          <t>PjBL Parte 2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-08-14T02:59:59Z</t>
+          <t>2026-10-31T02:59:59Z</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://pucpr.instructure.com/courses/71920/assignments/350693</t>
+          <t>https://pucpr.instructure.com/courses/71926/assignments/360142</t>
         </is>
       </c>
     </row>
@@ -1400,12 +1450,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Atividade Prática2 - Configuração de Rede - Hub e Switch (Packet Tracer)</t>
+          <t>TDE 1 - Trabalho Discente Efetivo</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-08-21T02:59:59Z</t>
+          <t>2026-09-14T02:59:59Z</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -1413,7 +1463,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://pucpr.instructure.com/courses/71920/assignments/352471</t>
+          <t>https://pucpr.instructure.com/courses/71920/assignments/342276</t>
         </is>
       </c>
     </row>
@@ -1425,12 +1475,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Atividade Prática3 - Configuração de Rede - Roteamento (Packet Tracer)</t>
+          <t>Atividade1 -  Wireshark</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-08-31T02:59:59Z</t>
+          <t>2026-08-14T02:59:59Z</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1438,7 +1488,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://pucpr.instructure.com/courses/71920/assignments/353858</t>
+          <t>https://pucpr.instructure.com/courses/71920/assignments/350693</t>
         </is>
       </c>
     </row>
@@ -1450,12 +1500,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Atividade Prática4 - Configuração de Rede - Topologia da Rede (Packet Tracer)</t>
+          <t>Atividade Prática2 - Configuração de Rede - Hub e Switch (Packet Tracer)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-09-07T02:59:59Z</t>
+          <t>2026-08-21T02:59:59Z</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1463,7 +1513,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://pucpr.instructure.com/courses/71920/assignments/356766</t>
+          <t>https://pucpr.instructure.com/courses/71920/assignments/352471</t>
         </is>
       </c>
     </row>
@@ -1475,12 +1525,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Atividade Prática 5 - Relatório Socket API</t>
+          <t>Atividade Prática3 - Configuração de Rede - Roteamento (Packet Tracer)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-09-18T02:59:59Z</t>
+          <t>2026-08-31T02:59:59Z</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1488,57 +1538,57 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://pucpr.instructure.com/courses/71920/assignments/357886</t>
+          <t>https://pucpr.instructure.com/courses/71920/assignments/353858</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Criptografia Aplicada</t>
+          <t>Conectividade e Sistemas Ciberfísicos</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SOMATIVA 1A: Modo de Blocos do Algoritmo AES (RA1)</t>
+          <t>Atividade Prática4 - Configuração de Rede - Topologia da Rede (Packet Tracer)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-09-09T02:59:59Z</t>
+          <t>2026-09-07T02:59:59Z</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://pucpr.instructure.com/courses/71912/assignments/338790</t>
+          <t>https://pucpr.instructure.com/courses/71920/assignments/356766</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Criptografia Aplicada</t>
+          <t>Conectividade e Sistemas Ciberfísicos</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SOMATIVA 1B: Negociação ECDH (RA1)</t>
+          <t>Atividade Prática 5 - Relatório Socket API</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-09-23T02:59:59Z</t>
+          <t>2026-09-18T02:59:59Z</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://pucpr.instructure.com/courses/71912/assignments/338791</t>
+          <t>https://pucpr.instructure.com/courses/71920/assignments/357886</t>
         </is>
       </c>
     </row>
@@ -1550,20 +1600,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SOMATIVA 1C: Modelo criptográfico híbrido do PGP (RA1)</t>
+          <t>SOMATIVA 1A: Modo de Blocos do Algoritmo AES (RA1)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-09-23T02:59:59Z</t>
+          <t>2026-09-09T02:59:59Z</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://pucpr.instructure.com/courses/71912/assignments/338792</t>
+          <t>https://pucpr.instructure.com/courses/71912/assignments/338790</t>
         </is>
       </c>
     </row>
@@ -1575,20 +1625,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Avaliação Teórica do RA1</t>
+          <t>SOMATIVA 1B: Negociação ECDH (RA1)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-09-22T12:40:00Z</t>
+          <t>2026-09-23T02:59:59Z</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://pucpr.instructure.com/courses/71912/assignments/358841</t>
+          <t>https://pucpr.instructure.com/courses/71912/assignments/338791</t>
         </is>
       </c>
     </row>
@@ -1600,15 +1650,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SOMATIVA 2A: Autenticação com SALT (RA2)</t>
+          <t>SOMATIVA 1C: Modelo criptográfico híbrido do PGP (RA1)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:59:59Z</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://pucpr.instructure.com/courses/71912/assignments/338793</t>
+          <t>https://pucpr.instructure.com/courses/71912/assignments/338792</t>
         </is>
       </c>
     </row>
@@ -1620,15 +1675,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SOMATIVA 2B: Autenticação Mútua e Challenge -SCRAM (RA 2)</t>
+          <t>Avaliação Teórica do RA1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-09-22T12:40:00Z</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://pucpr.instructure.com/courses/71912/assignments/338794</t>
+          <t>https://pucpr.instructure.com/courses/71912/assignments/358841</t>
         </is>
       </c>
     </row>
@@ -1640,15 +1700,15 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SOMATIVA 4: Aplicações com API TLS (RA2)</t>
+          <t>SOMATIVA 2A: Autenticação com SALT (RA2)</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://pucpr.instructure.com/courses/71912/assignments/338796</t>
+          <t>https://pucpr.instructure.com/courses/71912/assignments/338793</t>
         </is>
       </c>
     </row>
@@ -1660,15 +1720,15 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>TDE 1: Identificação por assinatura digital (RA3)</t>
+          <t>SOMATIVA 2B: Autenticação Mútua e Challenge -SCRAM (RA 2)</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://pucpr.instructure.com/courses/71912/assignments/338797</t>
+          <t>https://pucpr.instructure.com/courses/71912/assignments/338794</t>
         </is>
       </c>
     </row>
@@ -1680,15 +1740,15 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>TDE 2: Análise de uma captura HTTPS (RA3)</t>
+          <t>SOMATIVA 4: Aplicações com API TLS (RA2)</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://pucpr.instructure.com/courses/71912/assignments/338798</t>
+          <t>https://pucpr.instructure.com/courses/71912/assignments/338796</t>
         </is>
       </c>
     </row>
@@ -1700,13 +1760,53 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>TDE 1: Identificação por assinatura digital (RA3)</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>https://pucpr.instructure.com/courses/71912/assignments/338797</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Criptografia Aplicada</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>TDE 2: Análise de uma captura HTTPS (RA3)</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>https://pucpr.instructure.com/courses/71912/assignments/338798</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Criptografia Aplicada</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
           <t xml:space="preserve">SOMATIVA 3: Criação e uso de Certificados Digitais (RA 3) </t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="D21" t="n">
         <v>4</v>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>https://pucpr.instructure.com/courses/71912/assignments/338795</t>
         </is>

--- a/Painel_Academico_PUCPR.xlsx
+++ b/Painel_Academico_PUCPR.xlsx
@@ -907,12 +907,18 @@
           <t>2026-09-23T02:59:59Z</t>
         </is>
       </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
       <c r="D4" t="n">
         <v>3</v>
       </c>
+      <c r="E4" t="n">
+        <v>100</v>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Bom</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1235,19 +1241,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6">
@@ -1305,7 +1311,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1650,20 +1656,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SOMATIVA 1C: Modelo criptográfico híbrido do PGP (RA1)</t>
+          <t>Avaliação Teórica do RA1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-09-23T02:59:59Z</t>
+          <t>2026-09-22T12:40:00Z</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://pucpr.instructure.com/courses/71912/assignments/338792</t>
+          <t>https://pucpr.instructure.com/courses/71912/assignments/358841</t>
         </is>
       </c>
     </row>
@@ -1675,20 +1681,15 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Avaliação Teórica do RA1</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>2026-09-22T12:40:00Z</t>
+          <t>SOMATIVA 2A: Autenticação com SALT (RA2)</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://pucpr.instructure.com/courses/71912/assignments/358841</t>
+          <t>https://pucpr.instructure.com/courses/71912/assignments/338793</t>
         </is>
       </c>
     </row>
@@ -1700,15 +1701,15 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SOMATIVA 2A: Autenticação com SALT (RA2)</t>
+          <t>SOMATIVA 2B: Autenticação Mútua e Challenge -SCRAM (RA 2)</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://pucpr.instructure.com/courses/71912/assignments/338793</t>
+          <t>https://pucpr.instructure.com/courses/71912/assignments/338794</t>
         </is>
       </c>
     </row>
@@ -1720,15 +1721,15 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SOMATIVA 2B: Autenticação Mútua e Challenge -SCRAM (RA 2)</t>
+          <t>SOMATIVA 4: Aplicações com API TLS (RA2)</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://pucpr.instructure.com/courses/71912/assignments/338794</t>
+          <t>https://pucpr.instructure.com/courses/71912/assignments/338796</t>
         </is>
       </c>
     </row>
@@ -1740,15 +1741,15 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SOMATIVA 4: Aplicações com API TLS (RA2)</t>
+          <t>TDE 1: Identificação por assinatura digital (RA3)</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://pucpr.instructure.com/courses/71912/assignments/338796</t>
+          <t>https://pucpr.instructure.com/courses/71912/assignments/338797</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1761,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>TDE 1: Identificação por assinatura digital (RA3)</t>
+          <t>TDE 2: Análise de uma captura HTTPS (RA3)</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1768,7 +1769,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://pucpr.instructure.com/courses/71912/assignments/338797</t>
+          <t>https://pucpr.instructure.com/courses/71912/assignments/338798</t>
         </is>
       </c>
     </row>
@@ -1780,33 +1781,13 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>TDE 2: Análise de uma captura HTTPS (RA3)</t>
+          <t xml:space="preserve">SOMATIVA 3: Criação e uso de Certificados Digitais (RA 3) </t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E20" t="inlineStr">
-        <is>
-          <t>https://pucpr.instructure.com/courses/71912/assignments/338798</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Criptografia Aplicada</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SOMATIVA 3: Criação e uso de Certificados Digitais (RA 3) </t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>4</v>
-      </c>
-      <c r="E21" t="inlineStr">
         <is>
           <t>https://pucpr.instructure.com/courses/71912/assignments/338795</t>
         </is>
